--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/137.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/137.xlsx
@@ -426,13 +426,13 @@
         <v>-19.35008272732548</v>
       </c>
       <c r="E2">
-        <v>-12.09679242459922</v>
+        <v>-14.84257829746205</v>
       </c>
       <c r="F2">
-        <v>-1.345314476429508</v>
+        <v>-2.075734689836378</v>
       </c>
       <c r="G2">
-        <v>-5.481423685134445</v>
+        <v>-10.248781410053</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.01833198304989</v>
       </c>
       <c r="E3">
-        <v>-13.17427035914026</v>
+        <v>-16.48392370154217</v>
       </c>
       <c r="F3">
-        <v>-1.554023160495695</v>
+        <v>-2.431987751808566</v>
       </c>
       <c r="G3">
-        <v>-6.034331137830283</v>
+        <v>-9.412835555931629</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.54525424061365</v>
       </c>
       <c r="E4">
-        <v>-14.7208121598698</v>
+        <v>-15.16240177425377</v>
       </c>
       <c r="F4">
-        <v>-1.434713883503107</v>
+        <v>-1.834291596351014</v>
       </c>
       <c r="G4">
-        <v>-4.886084970261768</v>
+        <v>-9.802834373185471</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.96288938257845</v>
       </c>
       <c r="E5">
-        <v>-13.53328777846836</v>
+        <v>-16.51307801720355</v>
       </c>
       <c r="F5">
-        <v>-1.564035349293103</v>
+        <v>-2.257731006226848</v>
       </c>
       <c r="G5">
-        <v>-5.100032286282707</v>
+        <v>-9.167937949664042</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.26630226222881</v>
       </c>
       <c r="E6">
-        <v>-13.9902108058423</v>
+        <v>-16.22974045549163</v>
       </c>
       <c r="F6">
-        <v>-1.502588351627011</v>
+        <v>-2.577565166967591</v>
       </c>
       <c r="G6">
-        <v>-4.187361228743192</v>
+        <v>-8.322633183303155</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.48074663625641</v>
       </c>
       <c r="E7">
-        <v>-15.53541217826558</v>
+        <v>-18.54545715184601</v>
       </c>
       <c r="F7">
-        <v>-1.670990136439349</v>
+        <v>-2.586488557948134</v>
       </c>
       <c r="G7">
-        <v>-4.494351427145348</v>
+        <v>-7.931793487482339</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.62659272490319</v>
       </c>
       <c r="E8">
-        <v>-16.21087483277568</v>
+        <v>-18.9072414687928</v>
       </c>
       <c r="F8">
-        <v>-1.242456736486504</v>
+        <v>-2.680258993348346</v>
       </c>
       <c r="G8">
-        <v>-3.591383578581435</v>
+        <v>-6.273736549048218</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.73589167996109</v>
       </c>
       <c r="E9">
-        <v>-15.59655110584313</v>
+        <v>-19.51411585598273</v>
       </c>
       <c r="F9">
-        <v>-1.532804668640638</v>
+        <v>-2.299089486208549</v>
       </c>
       <c r="G9">
-        <v>-3.522249456084835</v>
+        <v>-6.227776245326516</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.84158366769073</v>
       </c>
       <c r="E10">
-        <v>-17.41043136961549</v>
+        <v>-19.32420071304905</v>
       </c>
       <c r="F10">
-        <v>-1.625368320133285</v>
+        <v>-2.356283441638729</v>
       </c>
       <c r="G10">
-        <v>-2.93766670366925</v>
+        <v>-6.728698201419179</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.97693757459372</v>
       </c>
       <c r="E11">
-        <v>-17.73333873720644</v>
+        <v>-21.58283599453674</v>
       </c>
       <c r="F11">
-        <v>-1.45938564610678</v>
+        <v>-2.263311985872857</v>
       </c>
       <c r="G11">
-        <v>-3.194757049157972</v>
+        <v>-7.048381031418901</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.18446441750851</v>
       </c>
       <c r="E12">
-        <v>-17.13341555761829</v>
+        <v>-21.02322981903887</v>
       </c>
       <c r="F12">
-        <v>-1.232294095627129</v>
+        <v>-2.621943774130035</v>
       </c>
       <c r="G12">
-        <v>-1.594088417647117</v>
+        <v>-5.268889972058774</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.49599725652969</v>
       </c>
       <c r="E13">
-        <v>-18.37646355882777</v>
+        <v>-22.13296407393655</v>
       </c>
       <c r="F13">
-        <v>-1.140737681096702</v>
+        <v>-1.667457680394961</v>
       </c>
       <c r="G13">
-        <v>-1.608154925643481</v>
+        <v>-5.703356036996107</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.9524122639238</v>
       </c>
       <c r="E14">
-        <v>-20.40364400530942</v>
+        <v>-23.63115988616021</v>
       </c>
       <c r="F14">
-        <v>-1.147603838093089</v>
+        <v>-1.45256541658194</v>
       </c>
       <c r="G14">
-        <v>-2.281486782875847</v>
+        <v>-5.056978641544486</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.56711560512275</v>
       </c>
       <c r="E15">
-        <v>-20.43588674024403</v>
+        <v>-23.70143727428524</v>
       </c>
       <c r="F15">
-        <v>-0.9296827367167905</v>
+        <v>-1.345939248413148</v>
       </c>
       <c r="G15">
-        <v>-1.098307738776943</v>
+        <v>-5.534230197031359</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.35195358437968</v>
       </c>
       <c r="E16">
-        <v>-20.68245762148767</v>
+        <v>-24.37705842538561</v>
       </c>
       <c r="F16">
-        <v>-0.616786791591588</v>
+        <v>-1.866346595932466</v>
       </c>
       <c r="G16">
-        <v>-1.045868697434887</v>
+        <v>-4.434251783425418</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.28677421557532</v>
       </c>
       <c r="E17">
-        <v>-22.51351438717113</v>
+        <v>-26.24099644083876</v>
       </c>
       <c r="F17">
-        <v>-0.3144486219516625</v>
+        <v>-1.608246083628511</v>
       </c>
       <c r="G17">
-        <v>-1.411058286417431</v>
+        <v>-3.664751888822763</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.35205558710631</v>
       </c>
       <c r="E18">
-        <v>-23.30832497415338</v>
+        <v>-27.02216273563591</v>
       </c>
       <c r="F18">
-        <v>-0.2606398379157341</v>
+        <v>-0.9795409663466551</v>
       </c>
       <c r="G18">
-        <v>-1.65367161626292</v>
+        <v>-4.09988006286795</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.50514691818131</v>
       </c>
       <c r="E19">
-        <v>-24.21412393058963</v>
+        <v>-27.15371490555873</v>
       </c>
       <c r="F19">
-        <v>0.1751603966301044</v>
+        <v>-0.8065638551446124</v>
       </c>
       <c r="G19">
-        <v>-0.9541533438149183</v>
+        <v>-4.728261332768093</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.71388979171738</v>
       </c>
       <c r="E20">
-        <v>-23.59860015804506</v>
+        <v>-27.1333865857383</v>
       </c>
       <c r="F20">
-        <v>0.7584511630808187</v>
+        <v>-0.2592358826216971</v>
       </c>
       <c r="G20">
-        <v>-0.5234613007923548</v>
+        <v>-4.499946249106716</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.9350511190259</v>
       </c>
       <c r="E21">
-        <v>-25.12853604458847</v>
+        <v>-27.44909820813105</v>
       </c>
       <c r="F21">
-        <v>0.7165558067937835</v>
+        <v>-0.7370336224861166</v>
       </c>
       <c r="G21">
-        <v>-1.102839875620205</v>
+        <v>-4.227991554146667</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.14230237690064</v>
       </c>
       <c r="E22">
-        <v>-26.50069083975663</v>
+        <v>-28.32760858019708</v>
       </c>
       <c r="F22">
-        <v>1.599646062301974</v>
+        <v>0.003580905898436939</v>
       </c>
       <c r="G22">
-        <v>-1.318154446948864</v>
+        <v>-2.551090990503014</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.30396218486598</v>
       </c>
       <c r="E23">
-        <v>-25.13006214032906</v>
+        <v>-28.94917333706789</v>
       </c>
       <c r="F23">
-        <v>1.153709318044365</v>
+        <v>0.2153002149098749</v>
       </c>
       <c r="G23">
-        <v>-1.12466630236062</v>
+        <v>-4.0346954211997</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.40451013997072</v>
       </c>
       <c r="E24">
-        <v>-25.33732133871211</v>
+        <v>-30.22765438315039</v>
       </c>
       <c r="F24">
-        <v>1.227899605359041</v>
+        <v>0.330932126766813</v>
       </c>
       <c r="G24">
-        <v>-1.067367380166914</v>
+        <v>-4.415547201128536</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.42550223664406</v>
       </c>
       <c r="E25">
-        <v>-25.45542394083215</v>
+        <v>-30.19865629984227</v>
       </c>
       <c r="F25">
-        <v>1.756056025922605</v>
+        <v>0.480874235428789</v>
       </c>
       <c r="G25">
-        <v>-1.192641733918475</v>
+        <v>-5.312234944804452</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.36592109689416</v>
       </c>
       <c r="E26">
-        <v>-26.99381448834789</v>
+        <v>-30.28211381156663</v>
       </c>
       <c r="F26">
-        <v>1.713394155972497</v>
+        <v>0.3465150011217795</v>
       </c>
       <c r="G26">
-        <v>-1.419450519359484</v>
+        <v>-4.510970365752489</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.22578599306894</v>
       </c>
       <c r="E27">
-        <v>-27.06538702003912</v>
+        <v>-31.57708529574806</v>
       </c>
       <c r="F27">
-        <v>1.609845128397404</v>
+        <v>0.6299445139843156</v>
       </c>
       <c r="G27">
-        <v>-1.845279370984858</v>
+        <v>-4.474630507367909</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.02028705123363</v>
       </c>
       <c r="E28">
-        <v>-26.0866932175014</v>
+        <v>-30.43777331286929</v>
       </c>
       <c r="F28">
-        <v>1.53269172731494</v>
+        <v>-0.2360258805779743</v>
       </c>
       <c r="G28">
-        <v>-1.655926097775164</v>
+        <v>-5.456703841592707</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.7654241856212</v>
       </c>
       <c r="E29">
-        <v>-25.68397602399928</v>
+        <v>-30.14042918105164</v>
       </c>
       <c r="F29">
-        <v>1.570649990696193</v>
+        <v>0.6735819467783342</v>
       </c>
       <c r="G29">
-        <v>-1.49686762679534</v>
+        <v>-4.822714507549039</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.4874535177345</v>
       </c>
       <c r="E30">
-        <v>-26.27253726230219</v>
+        <v>-30.5132901454212</v>
       </c>
       <c r="F30">
-        <v>1.63309551494197</v>
+        <v>0.3683519301368163</v>
       </c>
       <c r="G30">
-        <v>-2.081658943579899</v>
+        <v>-4.042001795204872</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.21076253146893</v>
       </c>
       <c r="E31">
-        <v>-25.18827114522365</v>
+        <v>-29.39206715196606</v>
       </c>
       <c r="F31">
-        <v>1.54733942332684</v>
+        <v>0.570770926159836</v>
       </c>
       <c r="G31">
-        <v>-1.140894596594128</v>
+        <v>-4.063109833563265</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.958644286651625</v>
       </c>
       <c r="E32">
-        <v>-24.90382863585386</v>
+        <v>-28.04639034432075</v>
       </c>
       <c r="F32">
-        <v>1.327270816729205</v>
+        <v>0.241832040111232</v>
       </c>
       <c r="G32">
-        <v>-1.806817452909605</v>
+        <v>-4.262255700478123</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.748272643563755</v>
       </c>
       <c r="E33">
-        <v>-24.99048098599063</v>
+        <v>-28.99357049623909</v>
       </c>
       <c r="F33">
-        <v>0.9051245027333277</v>
+        <v>0.3566340900684798</v>
       </c>
       <c r="G33">
-        <v>-2.05294989266334</v>
+        <v>-3.542625863879049</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.588884233605402</v>
       </c>
       <c r="E34">
-        <v>-23.87599636185891</v>
+        <v>-28.8544240754054</v>
       </c>
       <c r="F34">
-        <v>1.017884363912616</v>
+        <v>0.1527026548962153</v>
       </c>
       <c r="G34">
-        <v>-1.058965215588244</v>
+        <v>-4.068151794419575</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.486668474895888</v>
       </c>
       <c r="E35">
-        <v>-25.24089201319278</v>
+        <v>-28.30354879779432</v>
       </c>
       <c r="F35">
-        <v>1.019217844293416</v>
+        <v>0.1810937508422983</v>
       </c>
       <c r="G35">
-        <v>-2.011770016700345</v>
+        <v>-4.478844831839401</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.436482487168387</v>
       </c>
       <c r="E36">
-        <v>-23.61899187650159</v>
+        <v>-28.13011277177456</v>
       </c>
       <c r="F36">
-        <v>1.012187773734781</v>
+        <v>0.6080719515861814</v>
       </c>
       <c r="G36">
-        <v>-1.366908851105711</v>
+        <v>-4.737295811544763</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.434277093352888</v>
       </c>
       <c r="E37">
-        <v>-22.82487867451652</v>
+        <v>-25.94940347101086</v>
       </c>
       <c r="F37">
-        <v>0.8160188731070426</v>
+        <v>-0.0392979317620861</v>
       </c>
       <c r="G37">
-        <v>-0.9372265244726248</v>
+        <v>-3.585616608252025</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.465353387599755</v>
       </c>
       <c r="E38">
-        <v>-22.80500320209686</v>
+        <v>-27.18366623264546</v>
       </c>
       <c r="F38">
-        <v>1.316138947849581</v>
+        <v>-0.3191807352269956</v>
       </c>
       <c r="G38">
-        <v>-0.3864278892853025</v>
+        <v>-4.012491592267809</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.521755832868473</v>
       </c>
       <c r="E39">
-        <v>-22.68666511932841</v>
+        <v>-26.00444254410008</v>
       </c>
       <c r="F39">
-        <v>0.5336124342658803</v>
+        <v>0.2723603471902005</v>
       </c>
       <c r="G39">
-        <v>-1.060541035264937</v>
+        <v>-3.405172013088509</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.587984360777703</v>
       </c>
       <c r="E40">
-        <v>-22.07355955190393</v>
+        <v>-27.35435800341658</v>
       </c>
       <c r="F40">
-        <v>0.8741836402633871</v>
+        <v>-0.2348000921994241</v>
       </c>
       <c r="G40">
-        <v>-1.20302360472963</v>
+        <v>-3.168196542296399</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.659203973993311</v>
       </c>
       <c r="E41">
-        <v>-21.19798815946888</v>
+        <v>-26.41619404324751</v>
       </c>
       <c r="F41">
-        <v>1.311790091405785</v>
+        <v>0.2807793278366766</v>
       </c>
       <c r="G41">
-        <v>-0.6759715126954998</v>
+        <v>-3.473293108650092</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.723371450686784</v>
       </c>
       <c r="E42">
-        <v>-21.22169019242503</v>
+        <v>-24.91927073222001</v>
       </c>
       <c r="F42">
-        <v>0.4753930292554531</v>
+        <v>-0.08612574012275741</v>
       </c>
       <c r="G42">
-        <v>-0.7155192897076333</v>
+        <v>-2.632143076940991</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.780702099373631</v>
       </c>
       <c r="E43">
-        <v>-20.01842030689892</v>
+        <v>-24.85259800940509</v>
       </c>
       <c r="F43">
-        <v>0.9499908913177272</v>
+        <v>-0.6873353471537114</v>
       </c>
       <c r="G43">
-        <v>-0.6779743927467589</v>
+        <v>-4.399858525817931</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.82542567489538</v>
       </c>
       <c r="E44">
-        <v>-19.36869749864842</v>
+        <v>-24.9569883922299</v>
       </c>
       <c r="F44">
-        <v>0.8946767948091736</v>
+        <v>-0.2917073968589098</v>
       </c>
       <c r="G44">
-        <v>-0.7971672743426786</v>
+        <v>-3.592840218618714</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.864813370032206</v>
       </c>
       <c r="E45">
-        <v>-18.41249209803279</v>
+        <v>-24.56369948161175</v>
       </c>
       <c r="F45">
-        <v>0.8883720615598092</v>
+        <v>0.3296152752981251</v>
       </c>
       <c r="G45">
-        <v>-1.240058677677457</v>
+        <v>-4.322371896925749</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.899000324386995</v>
       </c>
       <c r="E46">
-        <v>-18.04960736190214</v>
+        <v>-24.32136725203928</v>
       </c>
       <c r="F46">
-        <v>0.9730464820346947</v>
+        <v>-0.06952691842303656</v>
       </c>
       <c r="G46">
-        <v>-0.9139368366038519</v>
+        <v>-3.552352246673428</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.938700892340167</v>
       </c>
       <c r="E47">
-        <v>-18.35409289722988</v>
+        <v>-21.17091694185103</v>
       </c>
       <c r="F47">
-        <v>0.6897056567034231</v>
+        <v>-0.3681924740450579</v>
       </c>
       <c r="G47">
-        <v>-0.8149415933430256</v>
+        <v>-3.481357597583757</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.985722569612717</v>
       </c>
       <c r="E48">
-        <v>-17.91360823050378</v>
+        <v>-23.77057348696034</v>
       </c>
       <c r="F48">
-        <v>1.195025037966349</v>
+        <v>0.2064029550769361</v>
       </c>
       <c r="G48">
-        <v>-0.8940470790039107</v>
+        <v>-4.163012166301852</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.05259748300801</v>
       </c>
       <c r="E49">
-        <v>-16.53310745773948</v>
+        <v>-22.44066029733573</v>
       </c>
       <c r="F49">
-        <v>0.7799357175296702</v>
+        <v>-0.5853209306106794</v>
       </c>
       <c r="G49">
-        <v>-0.7700638380126654</v>
+        <v>-4.658577659711973</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.14339934942859</v>
       </c>
       <c r="E50">
-        <v>-16.38368592938239</v>
+        <v>-22.62123772686559</v>
       </c>
       <c r="F50">
-        <v>0.7682052078140102</v>
+        <v>-0.4657044146704956</v>
       </c>
       <c r="G50">
-        <v>-1.401927801820121</v>
+        <v>-4.638356847558105</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.27147828072862</v>
       </c>
       <c r="E51">
-        <v>-16.45381840633918</v>
+        <v>-21.11925158189752</v>
       </c>
       <c r="F51">
-        <v>0.8156324488636754</v>
+        <v>0.3300848441020529</v>
       </c>
       <c r="G51">
-        <v>-0.993151570267533</v>
+        <v>-4.663215734012493</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.43883613386596</v>
       </c>
       <c r="E52">
-        <v>-15.51036518852915</v>
+        <v>-22.26557137830316</v>
       </c>
       <c r="F52">
-        <v>0.7532756121491626</v>
+        <v>-0.3009625742287379</v>
       </c>
       <c r="G52">
-        <v>-0.6984534274526905</v>
+        <v>-3.84214416099907</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.65118639108536</v>
       </c>
       <c r="E53">
-        <v>-16.17926155572813</v>
+        <v>-20.24237598894826</v>
       </c>
       <c r="F53">
-        <v>0.9170846498067263</v>
+        <v>-0.03062714187505513</v>
       </c>
       <c r="G53">
-        <v>-0.5481943865162497</v>
+        <v>-3.334319717457027</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.90270987273168</v>
       </c>
       <c r="E54">
-        <v>-15.08523657716307</v>
+        <v>-21.34907163778679</v>
       </c>
       <c r="F54">
-        <v>0.7591654144486819</v>
+        <v>0.0257527887145892</v>
       </c>
       <c r="G54">
-        <v>-1.249073293180892</v>
+        <v>-4.951951584311107</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.18936271793516</v>
       </c>
       <c r="E55">
-        <v>-15.12531357213095</v>
+        <v>-19.35102739307049</v>
       </c>
       <c r="F55">
-        <v>0.6959248698333539</v>
+        <v>0.1558946141687835</v>
       </c>
       <c r="G55">
-        <v>-1.750501762741063</v>
+        <v>-3.691852014607237</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.50136225013199</v>
       </c>
       <c r="E56">
-        <v>-13.63554072156156</v>
+        <v>-18.21293130546277</v>
       </c>
       <c r="F56">
-        <v>0.793189752335983</v>
+        <v>-0.4678004494495797</v>
       </c>
       <c r="G56">
-        <v>-1.636566027461506</v>
+        <v>-3.702690740702811</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.83040132125407</v>
       </c>
       <c r="E57">
-        <v>-14.84971970097215</v>
+        <v>-18.50945578348503</v>
       </c>
       <c r="F57">
-        <v>0.8507764668331922</v>
+        <v>-0.1913408263208925</v>
       </c>
       <c r="G57">
-        <v>-2.072217267701898</v>
+        <v>-4.846447808520074</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.16984945487794</v>
       </c>
       <c r="E58">
-        <v>-14.12910363213156</v>
+        <v>-17.32761010848921</v>
       </c>
       <c r="F58">
-        <v>0.4238370668842373</v>
+        <v>-0.3809880259888509</v>
       </c>
       <c r="G58">
-        <v>-2.075971426343431</v>
+        <v>-4.773638980474883</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.51078487781791</v>
       </c>
       <c r="E59">
-        <v>-14.36833385700877</v>
+        <v>-18.87513005960441</v>
       </c>
       <c r="F59">
-        <v>1.076758631319078</v>
+        <v>-0.1080687774341287</v>
       </c>
       <c r="G59">
-        <v>-1.522004599075027</v>
+        <v>-4.524215858455113</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.84932677359689</v>
       </c>
       <c r="E60">
-        <v>-13.66892463194611</v>
+        <v>-16.64892770895965</v>
       </c>
       <c r="F60">
-        <v>0.4954142394384386</v>
+        <v>0.08239719819211191</v>
       </c>
       <c r="G60">
-        <v>-2.371308504447353</v>
+        <v>-5.31060615639913</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.17391416402565</v>
       </c>
       <c r="E61">
-        <v>-13.8140350530479</v>
+        <v>-19.17217984061156</v>
       </c>
       <c r="F61">
-        <v>1.011584381780998</v>
+        <v>0.1921630633382623</v>
       </c>
       <c r="G61">
-        <v>-2.180852819573082</v>
+        <v>-5.209823218547097</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.48026186803762</v>
       </c>
       <c r="E62">
-        <v>-13.73370445262583</v>
+        <v>-17.36181820114315</v>
       </c>
       <c r="F62">
-        <v>0.8220971364104992</v>
+        <v>-0.1107103989010817</v>
       </c>
       <c r="G62">
-        <v>-1.809691006437693</v>
+        <v>-4.606052544185896</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.75405555003178</v>
       </c>
       <c r="E63">
-        <v>-14.37105999836139</v>
+        <v>-16.48656833036265</v>
       </c>
       <c r="F63">
-        <v>0.6326463162760553</v>
+        <v>0.2810731052839906</v>
       </c>
       <c r="G63">
-        <v>-1.474345985491679</v>
+        <v>-4.885618183340731</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.99316812978106</v>
       </c>
       <c r="E64">
-        <v>-12.72926627535451</v>
+        <v>-16.16523687172638</v>
       </c>
       <c r="F64">
-        <v>0.3827288124371755</v>
+        <v>-0.05556496707252238</v>
       </c>
       <c r="G64">
-        <v>-2.430610306692318</v>
+        <v>-5.499565474689651</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.18499431234893</v>
       </c>
       <c r="E65">
-        <v>-13.60061713001441</v>
+        <v>-15.93994528984478</v>
       </c>
       <c r="F65">
-        <v>0.8154233996828374</v>
+        <v>-0.7432773830577366</v>
       </c>
       <c r="G65">
-        <v>-3.167567538643937</v>
+        <v>-5.756688925633766</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.33199042286127</v>
       </c>
       <c r="E66">
-        <v>-12.52448415225365</v>
+        <v>-16.40592526523406</v>
       </c>
       <c r="F66">
-        <v>0.3240406304757782</v>
+        <v>-0.297297878740411</v>
       </c>
       <c r="G66">
-        <v>-2.068833890160763</v>
+        <v>-6.329949612305043</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.42744874206442</v>
       </c>
       <c r="E67">
-        <v>-12.71306339535506</v>
+        <v>-16.09543950184615</v>
       </c>
       <c r="F67">
-        <v>0.5935984632249802</v>
+        <v>-1.240907872101204</v>
       </c>
       <c r="G67">
-        <v>-3.031755718440877</v>
+        <v>-4.913714783332526</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.47989548248778</v>
       </c>
       <c r="E68">
-        <v>-13.14257104108657</v>
+        <v>-16.1345519318504</v>
       </c>
       <c r="F68">
-        <v>0.1116070700964771</v>
+        <v>-0.2491666804113331</v>
       </c>
       <c r="G68">
-        <v>-2.790416948628007</v>
+        <v>-6.304898714209378</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.48957505797332</v>
       </c>
       <c r="E69">
-        <v>-13.60594714392144</v>
+        <v>-15.87724856720858</v>
       </c>
       <c r="F69">
-        <v>0.09327013115456144</v>
+        <v>-0.7395730949215238</v>
       </c>
       <c r="G69">
-        <v>-3.175877007947508</v>
+        <v>-5.825740284491884</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.46814297386523</v>
       </c>
       <c r="E70">
-        <v>-12.82858023881673</v>
+        <v>-15.20969715678988</v>
       </c>
       <c r="F70">
-        <v>0.3852231492539927</v>
+        <v>-0.3223790293232256</v>
       </c>
       <c r="G70">
-        <v>-3.865367637957058</v>
+        <v>-5.319865752272472</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.4184238727343</v>
       </c>
       <c r="E71">
-        <v>-12.55765069588583</v>
+        <v>-16.83385247353688</v>
       </c>
       <c r="F71">
-        <v>0.5092684987867029</v>
+        <v>-1.161803345330919</v>
       </c>
       <c r="G71">
-        <v>-1.885214481825086</v>
+        <v>-6.249410660425653</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.34860861206899</v>
       </c>
       <c r="E72">
-        <v>-12.45628986217214</v>
+        <v>-16.00353412186048</v>
       </c>
       <c r="F72">
-        <v>0.361179326045791</v>
+        <v>-0.5017170953346308</v>
       </c>
       <c r="G72">
-        <v>-2.340374766928403</v>
+        <v>-6.197395368912624</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.26180233632016</v>
       </c>
       <c r="E73">
-        <v>-11.57829120766898</v>
+        <v>-15.94029851081737</v>
       </c>
       <c r="F73">
-        <v>0.2624661444834925</v>
+        <v>-0.2324958000924597</v>
       </c>
       <c r="G73">
-        <v>-2.443021541919046</v>
+        <v>-6.19582617032701</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.16186829283709</v>
       </c>
       <c r="E74">
-        <v>-12.16760417265716</v>
+        <v>-17.3632627843516</v>
       </c>
       <c r="F74">
-        <v>0.3150831898180527</v>
+        <v>-0.8739172840223367</v>
       </c>
       <c r="G74">
-        <v>-2.549677387557745</v>
+        <v>-5.878517001478945</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.05429677504782</v>
       </c>
       <c r="E75">
-        <v>-12.65721825389247</v>
+        <v>-16.15408324024548</v>
       </c>
       <c r="F75">
-        <v>-0.1119512324858285</v>
+        <v>-1.044775396709521</v>
       </c>
       <c r="G75">
-        <v>-1.997408870150987</v>
+        <v>-3.793065323379375</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.94071322239272</v>
       </c>
       <c r="E76">
-        <v>-13.14764746044917</v>
+        <v>-17.2603577410013</v>
       </c>
       <c r="F76">
-        <v>0.129251137700388</v>
+        <v>-1.36970513123319</v>
       </c>
       <c r="G76">
-        <v>-2.167627190143694</v>
+        <v>-4.767627029775566</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.82870550259369</v>
       </c>
       <c r="E77">
-        <v>-13.86011227607594</v>
+        <v>-17.51138011219448</v>
       </c>
       <c r="F77">
-        <v>0.2074173187157751</v>
+        <v>-0.4850889750754744</v>
       </c>
       <c r="G77">
-        <v>-1.48692274799537</v>
+        <v>-5.126119385132164</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.71815987014841</v>
       </c>
       <c r="E78">
-        <v>-13.14120344193625</v>
+        <v>-17.11704512408055</v>
       </c>
       <c r="F78">
-        <v>0.2344456357216224</v>
+        <v>-1.072596358526046</v>
       </c>
       <c r="G78">
-        <v>-1.470495821029506</v>
+        <v>-3.924838278024525</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.61849648244747</v>
       </c>
       <c r="E79">
-        <v>-13.35072687732314</v>
+        <v>-17.56660032424401</v>
       </c>
       <c r="F79">
-        <v>-0.236385381820779</v>
+        <v>-0.9383780740455108</v>
       </c>
       <c r="G79">
-        <v>-1.44145240501348</v>
+        <v>-4.715432968803417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.52754482461801</v>
       </c>
       <c r="E80">
-        <v>-14.42959958185854</v>
+        <v>-18.66727763112635</v>
       </c>
       <c r="F80">
-        <v>-0.364816013033341</v>
+        <v>-1.461297970999673</v>
       </c>
       <c r="G80">
-        <v>-1.632891321912915</v>
+        <v>-3.671065099166153</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.45385916807148</v>
       </c>
       <c r="E81">
-        <v>-14.30993012773185</v>
+        <v>-18.5074315556036</v>
       </c>
       <c r="F81">
-        <v>-0.5382555663626921</v>
+        <v>-1.448299704698704</v>
       </c>
       <c r="G81">
-        <v>-0.4387179560780909</v>
+        <v>-4.862063651828816</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.39245826331472</v>
       </c>
       <c r="E82">
-        <v>-15.54741716285991</v>
+        <v>-18.85228390823572</v>
       </c>
       <c r="F82">
-        <v>-0.6115265123934558</v>
+        <v>-1.926772895136059</v>
       </c>
       <c r="G82">
-        <v>0.2157272388527337</v>
+        <v>-3.97728394045766</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.34989275928822</v>
       </c>
       <c r="E83">
-        <v>-16.10407077330477</v>
+        <v>-20.63576452599458</v>
       </c>
       <c r="F83">
-        <v>-0.2852577545182827</v>
+        <v>-2.016232483034444</v>
       </c>
       <c r="G83">
-        <v>-0.530373719878353</v>
+        <v>-3.618275139996935</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.31899995134618</v>
       </c>
       <c r="E84">
-        <v>-16.97273171440412</v>
+        <v>-19.47654763561509</v>
       </c>
       <c r="F84">
-        <v>-0.6442514195771388</v>
+        <v>-1.576651942468452</v>
       </c>
       <c r="G84">
-        <v>-0.2143589743361433</v>
+        <v>-3.276405033793017</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.30528403256251</v>
       </c>
       <c r="E85">
-        <v>-18.1614063282035</v>
+        <v>-21.13139242071208</v>
       </c>
       <c r="F85">
-        <v>-0.6334956808524319</v>
+        <v>-1.398502447746584</v>
       </c>
       <c r="G85">
-        <v>0.8219510274585342</v>
+        <v>-3.457806376617382</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.30123523091593</v>
       </c>
       <c r="E86">
-        <v>-19.88236683381248</v>
+        <v>-21.06981875962979</v>
       </c>
       <c r="F86">
-        <v>-0.5559099280550533</v>
+        <v>-1.640197350472502</v>
       </c>
       <c r="G86">
-        <v>0.530272102175507</v>
+        <v>-3.596951916178489</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.31027266514799</v>
       </c>
       <c r="E87">
-        <v>-19.87161170804426</v>
+        <v>-23.79255469979358</v>
       </c>
       <c r="F87">
-        <v>-0.8521579565971563</v>
+        <v>-1.919551196161655</v>
       </c>
       <c r="G87">
-        <v>0.08185870888122473</v>
+        <v>-3.015924689672082</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.32473785986681</v>
       </c>
       <c r="E88">
-        <v>-20.9015678363488</v>
+        <v>-25.39044486729609</v>
       </c>
       <c r="F88">
-        <v>-1.238709688290574</v>
+        <v>-1.729067007917386</v>
       </c>
       <c r="G88">
-        <v>0.3963141874744377</v>
+        <v>-3.139153126280373</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.34695243329678</v>
       </c>
       <c r="E89">
-        <v>-23.37139756013222</v>
+        <v>-26.87712477011824</v>
       </c>
       <c r="F89">
-        <v>-1.44871067638376</v>
+        <v>-2.142255881255538</v>
       </c>
       <c r="G89">
-        <v>0.5661253103658139</v>
+        <v>-3.799457986815708</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.37028392343693</v>
       </c>
       <c r="E90">
-        <v>-25.23380495137078</v>
+        <v>-27.46367536596174</v>
       </c>
       <c r="F90">
-        <v>-1.57761087640025</v>
+        <v>-2.40592787097001</v>
       </c>
       <c r="G90">
-        <v>0.4240002798193626</v>
+        <v>-1.786116611652543</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.39338083631816</v>
       </c>
       <c r="E91">
-        <v>-25.71725577948165</v>
+        <v>-29.78596061386424</v>
       </c>
       <c r="F91">
-        <v>-1.803183652906995</v>
+        <v>-2.258697858688224</v>
       </c>
       <c r="G91">
-        <v>0.01381375586704475</v>
+        <v>-3.605794383313882</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.40912454814452</v>
       </c>
       <c r="E92">
-        <v>-27.31789020223281</v>
+        <v>-31.51720301970763</v>
       </c>
       <c r="F92">
-        <v>-1.856409633166042</v>
+        <v>-2.382915040312759</v>
       </c>
       <c r="G92">
-        <v>0.1201253047696604</v>
+        <v>-3.876299059327731</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.41054771413596</v>
       </c>
       <c r="E93">
-        <v>-29.36552576580711</v>
+        <v>-31.26762296748589</v>
       </c>
       <c r="F93">
-        <v>-1.991567055254433</v>
+        <v>-2.566128434699245</v>
       </c>
       <c r="G93">
-        <v>0.09227699569331116</v>
+        <v>-3.871154471559704</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.38974440900405</v>
       </c>
       <c r="E94">
-        <v>-32.12249923370589</v>
+        <v>-34.86009309708884</v>
       </c>
       <c r="F94">
-        <v>-2.276581857738324</v>
+        <v>-3.008472542087679</v>
       </c>
       <c r="G94">
-        <v>-0.2964836775288436</v>
+        <v>-4.163462400495193</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.33802120102309</v>
       </c>
       <c r="E95">
-        <v>-33.91965584296792</v>
+        <v>-35.37349525228645</v>
       </c>
       <c r="F95">
-        <v>-2.863887318684677</v>
+        <v>-2.978584844051506</v>
       </c>
       <c r="G95">
-        <v>-1.877053987070783</v>
+        <v>-3.573844308314376</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.25070461804248</v>
       </c>
       <c r="E96">
-        <v>-35.33994831683762</v>
+        <v>-38.42973745345613</v>
       </c>
       <c r="F96">
-        <v>-3.208438377647683</v>
+        <v>-3.52669120803186</v>
       </c>
       <c r="G96">
-        <v>-0.9406728023790061</v>
+        <v>-3.982537776228483</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.12312521764505</v>
       </c>
       <c r="E97">
-        <v>-36.86332923725494</v>
+        <v>-39.11125694195149</v>
       </c>
       <c r="F97">
-        <v>-2.999542024430516</v>
+        <v>-3.378961536533752</v>
       </c>
       <c r="G97">
-        <v>-1.157705546842547</v>
+        <v>-4.908364941741063</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.95698940621082</v>
       </c>
       <c r="E98">
-        <v>-40.97922529927146</v>
+        <v>-42.15445487374208</v>
       </c>
       <c r="F98">
-        <v>-3.48884301221173</v>
+        <v>-3.806561341849446</v>
       </c>
       <c r="G98">
-        <v>-1.436400512520552</v>
+        <v>-4.7104241134025</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.75761369705782</v>
       </c>
       <c r="E99">
-        <v>-42.51504140931384</v>
+        <v>-43.62982491273007</v>
       </c>
       <c r="F99">
-        <v>-3.652321847185925</v>
+        <v>-4.268948831303682</v>
       </c>
       <c r="G99">
-        <v>-1.650579566729241</v>
+        <v>-5.394111357081706</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.53045572330898</v>
       </c>
       <c r="E100">
-        <v>-45.48692040395763</v>
+        <v>-45.94827907162208</v>
       </c>
       <c r="F100">
-        <v>-3.911628351544487</v>
+        <v>-4.048781243086331</v>
       </c>
       <c r="G100">
-        <v>-1.675352378999607</v>
+        <v>-5.500561948896972</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.29434490824776</v>
       </c>
       <c r="E101">
-        <v>-46.93948278360599</v>
+        <v>-49.56069373287331</v>
       </c>
       <c r="F101">
-        <v>-4.424271580813363</v>
+        <v>-4.661533690681966</v>
       </c>
       <c r="G101">
-        <v>-2.673812913643797</v>
+        <v>-5.817285151184585</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.04730821129083</v>
       </c>
       <c r="E102">
-        <v>-49.96086705610163</v>
+        <v>-53.09883009921373</v>
       </c>
       <c r="F102">
-        <v>-4.425419767602056</v>
+        <v>-4.673011599304114</v>
       </c>
       <c r="G102">
-        <v>-3.04523294933125</v>
+        <v>-6.756152555576355</v>
       </c>
     </row>
   </sheetData>
